--- a/tasks/finalpool/canvas-course-comparison/groundtruth_workspace/Canvas_Course_Comparison.xlsx
+++ b/tasks/finalpool/canvas-course-comparison/groundtruth_workspace/Canvas_Course_Comparison.xlsx
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
